--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R4" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000516</v>
+        <v>129000520</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>841140</v>
+        <v>840958</v>
       </c>
       <c r="R5" t="n">
-        <v>7466925</v>
+        <v>7466803</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000527</v>
       </c>
       <c r="B2" t="n">
-        <v>91727</v>
+        <v>91730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000514</v>
       </c>
       <c r="B3" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000516</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000520</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000522</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000517</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129000521</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>129000525</v>
       </c>
       <c r="B11" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000516</v>
+        <v>129000520</v>
       </c>
       <c r="B4" t="n">
         <v>79043</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>841140</v>
+        <v>840958</v>
       </c>
       <c r="R4" t="n">
-        <v>7466925</v>
+        <v>7466803</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B5" t="n">
         <v>79043</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R5" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000527</v>
       </c>
       <c r="B2" t="n">
-        <v>91730</v>
+        <v>91732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000514</v>
       </c>
       <c r="B3" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000520</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000516</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000522</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000517</v>
       </c>
       <c r="B8" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>129000521</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>129000525</v>
       </c>
       <c r="B11" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000527</v>
       </c>
       <c r="B2" t="n">
-        <v>91732</v>
+        <v>91736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R4" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000516</v>
+        <v>129000520</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>841140</v>
+        <v>840958</v>
       </c>
       <c r="R5" t="n">
-        <v>7466925</v>
+        <v>7466803</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1314,7 +1314,7 @@
         <v>129000517</v>
       </c>
       <c r="B8" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000527</v>
       </c>
       <c r="B2" t="n">
-        <v>91736</v>
+        <v>91737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000522</v>
+        <v>129000523</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>840853</v>
+        <v>840827</v>
       </c>
       <c r="R6" t="n">
-        <v>7467091</v>
+        <v>7467150</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,37 +1205,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000523</v>
+        <v>129000522</v>
       </c>
       <c r="B7" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>840827</v>
+        <v>840853</v>
       </c>
       <c r="R7" t="n">
-        <v>7467150</v>
+        <v>7467091</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,7 +1314,7 @@
         <v>129000517</v>
       </c>
       <c r="B8" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000516</v>
+        <v>129000520</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>841140</v>
+        <v>840958</v>
       </c>
       <c r="R4" t="n">
-        <v>7466925</v>
+        <v>7466803</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R5" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000527</v>
       </c>
       <c r="B2" t="n">
-        <v>91737</v>
+        <v>91740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R4" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000516</v>
+        <v>129000520</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>841140</v>
+        <v>840958</v>
       </c>
       <c r="R5" t="n">
-        <v>7466925</v>
+        <v>7466803</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,37 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000523</v>
+        <v>129000522</v>
       </c>
       <c r="B6" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>840827</v>
+        <v>840853</v>
       </c>
       <c r="R6" t="n">
-        <v>7467150</v>
+        <v>7467091</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,37 +1205,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000522</v>
+        <v>129000523</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>840853</v>
+        <v>840827</v>
       </c>
       <c r="R7" t="n">
-        <v>7467091</v>
+        <v>7467150</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,7 +1314,7 @@
         <v>129000517</v>
       </c>
       <c r="B8" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000527</v>
+        <v>129000514</v>
       </c>
       <c r="B2" t="n">
-        <v>91740</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>840806</v>
+        <v>841236</v>
       </c>
       <c r="R2" t="n">
-        <v>7467181</v>
+        <v>7466905</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000514</v>
+        <v>129000525</v>
       </c>
       <c r="B3" t="n">
-        <v>82878</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>841236</v>
+        <v>840806</v>
       </c>
       <c r="R3" t="n">
-        <v>7466905</v>
+        <v>7467180</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000516</v>
+        <v>129000527</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>841140</v>
+        <v>840806</v>
       </c>
       <c r="R4" t="n">
-        <v>7466925</v>
+        <v>7467181</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,14 +993,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000520</v>
+        <v>129000516</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>840958</v>
+        <v>841140</v>
       </c>
       <c r="R5" t="n">
-        <v>7466803</v>
+        <v>7466925</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,14 +1099,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000522</v>
+        <v>129000520</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>840853</v>
+        <v>840958</v>
       </c>
       <c r="R6" t="n">
-        <v>7467091</v>
+        <v>7466803</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000523</v>
+        <v>129000521</v>
       </c>
       <c r="B7" t="n">
-        <v>58097</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>840827</v>
+        <v>840981</v>
       </c>
       <c r="R7" t="n">
-        <v>7467150</v>
+        <v>7466926</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,33 +1311,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000517</v>
+        <v>129000522</v>
       </c>
       <c r="B8" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1346,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>841043</v>
+        <v>840853</v>
       </c>
       <c r="R8" t="n">
-        <v>7466884</v>
+        <v>7467091</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1413,14 +1417,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000521</v>
+        <v>129000528</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1452,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>840981</v>
+        <v>840790</v>
       </c>
       <c r="R9" t="n">
-        <v>7466926</v>
+        <v>7467176</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1522,7 +1526,7 @@
         <v>129000515</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,37 +1629,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000525</v>
+        <v>129000523</v>
       </c>
       <c r="B11" t="n">
-        <v>82878</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1664,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>840806</v>
+        <v>840827</v>
       </c>
       <c r="R11" t="n">
-        <v>7467180</v>
+        <v>7467150</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 53440-2025 artfynd.xlsx
+++ b/artfynd/A 53440-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000525</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000521</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000528</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,8 +1782,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>